--- a/docs/downloads/13/tbl_synthese_qualite_marovoay_tous.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_marovoay_tous.xlsx
@@ -392,9 +392,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D2">
-        <v>2</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -432,9 +429,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D4">
-        <v>3</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -512,9 +506,6 @@
           <t>Mefiant</t>
         </is>
       </c>
-      <c r="D8">
-        <v>3</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -572,9 +563,6 @@
           <t>Neutre</t>
         </is>
       </c>
-      <c r="D11">
-        <v>1</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -671,9 +659,6 @@
         <is>
           <t>Neutre</t>
         </is>
-      </c>
-      <c r="D16">
-        <v>3</v>
       </c>
     </row>
     <row r="17">

--- a/docs/downloads/13/tbl_synthese_qualite_marovoay_tous.xlsx
+++ b/docs/downloads/13/tbl_synthese_qualite_marovoay_tous.xlsx
@@ -379,7 +379,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -396,7 +396,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -416,7 +416,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -433,7 +433,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -453,7 +453,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Marovoay - Ampijoroa</t>
+          <t>Ampijoroa</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -473,7 +473,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -493,7 +493,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -510,7 +510,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -530,7 +530,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Marovoay - Bepako</t>
+          <t>Bepako</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -550,7 +550,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -567,7 +567,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -587,7 +587,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -607,7 +607,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -627,7 +627,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Marovoay - Madiromiongana</t>
+          <t>Madiromiongana</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -647,7 +647,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -664,7 +664,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -684,7 +684,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -704,7 +704,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -724,7 +724,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Marovoay - Maroala</t>
+          <t>Maroala</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -744,7 +744,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -764,7 +764,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -784,7 +784,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -804,7 +804,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -824,7 +824,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Marovoay - Tous</t>
+          <t>Tous</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
